--- a/db_specs/tpk_table_spec_20260321.xlsx
+++ b/db_specs/tpk_table_spec_20260321.xlsx
@@ -5,32 +5,34 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsshim\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\tpk_mvp\db_specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D89B508-D2F6-45A7-BC20-8C0B9D8CE6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323CAD56-5039-4A7B-8423-FCD7E36D6509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="tb_user" sheetId="1" r:id="rId1"/>
-    <sheet name="tb_user_device" sheetId="2" r:id="rId2"/>
-    <sheet name="tb_exam_list" sheetId="3" r:id="rId3"/>
-    <sheet name="tb_exam_instruction" sheetId="4" r:id="rId4"/>
-    <sheet name="tb_exam_question" sheetId="5" r:id="rId5"/>
-    <sheet name="tb_exam_answer" sheetId="6" r:id="rId6"/>
-    <sheet name="tb_practice_question" sheetId="7" r:id="rId7"/>
-    <sheet name="tb_practice_answer" sheetId="8" r:id="rId8"/>
-    <sheet name="tb_question_structure" sheetId="9" r:id="rId9"/>
-    <sheet name="tb_history_exam" sheetId="10" r:id="rId10"/>
-    <sheet name="tb_history_practice" sheetId="11" r:id="rId11"/>
+    <sheet name="tb_group_code" sheetId="12" r:id="rId1"/>
+    <sheet name="tb_code" sheetId="13" r:id="rId2"/>
+    <sheet name="tb_user" sheetId="1" r:id="rId3"/>
+    <sheet name="tb_user_device" sheetId="2" r:id="rId4"/>
+    <sheet name="tb_exam_list" sheetId="3" r:id="rId5"/>
+    <sheet name="tb_exam_instruction" sheetId="4" r:id="rId6"/>
+    <sheet name="tb_exam_question" sheetId="5" r:id="rId7"/>
+    <sheet name="tb_exam_answer" sheetId="6" r:id="rId8"/>
+    <sheet name="tb_practice_question" sheetId="7" r:id="rId9"/>
+    <sheet name="tb_practice_answer" sheetId="8" r:id="rId10"/>
+    <sheet name="tb_question_structure" sheetId="9" r:id="rId11"/>
+    <sheet name="tb_history_exam" sheetId="10" r:id="rId12"/>
+    <sheet name="tb_history_practice" sheetId="11" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="145">
   <si>
     <t>tb_user : 사용자</t>
   </si>
@@ -404,6 +406,77 @@
   <si>
     <t>PK_EXAM_INSTRUCTION</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tb_group_code : 그룹코드</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_code</t>
+  </si>
+  <si>
+    <t>그룹코드</t>
+  </si>
+  <si>
+    <t>PK_GROUP_CODE</t>
+  </si>
+  <si>
+    <t>group_name</t>
+  </si>
+  <si>
+    <t>그룹코드명</t>
+  </si>
+  <si>
+    <t>group_desc</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>생성시간</t>
+  </si>
+  <si>
+    <t>수정시간</t>
+  </si>
+  <si>
+    <t>tb_code : 코드</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PK_CODE</t>
+  </si>
+  <si>
+    <t>TB_GROUP_CODE</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>코드</t>
+  </si>
+  <si>
+    <t>code_name</t>
+  </si>
+  <si>
+    <t>코드명</t>
+  </si>
+  <si>
+    <t>code_desc</t>
+  </si>
+  <si>
+    <t>코드설명</t>
+  </si>
+  <si>
+    <t>sort_order</t>
+  </si>
+  <si>
+    <t>소스순서</t>
+  </si>
+  <si>
+    <t>SMALLINT</t>
   </si>
 </sst>
 </file>
@@ -487,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -501,6 +574,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -802,9 +876,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C188A5-A1AF-4F10-B69D-FC35BDC4C50F}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -817,12 +891,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -857,17 +931,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D3" s="4">
+        <v>20</v>
+      </c>
       <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
@@ -876,24 +952,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>15</v>
@@ -905,18 +981,18 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
@@ -926,45 +1002,47 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="4">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3"/>
@@ -972,22 +1050,24 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D8" s="4">
+        <v>50</v>
+      </c>
       <c r="E8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
@@ -995,24 +1075,22 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4">
-        <v>50</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
@@ -1020,53 +1098,30 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D10" s="4">
+        <v>50</v>
+      </c>
       <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4">
-        <v>50</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1075,9 +1130,243 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="5" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>50</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -1090,12 +1379,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1130,12 +1419,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -1149,170 +1438,160 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D4" s="4">
+        <v>50</v>
+      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I4" s="4"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I5" s="4"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I6" s="4"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="4">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="3"/>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
@@ -1320,101 +1599,30 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D11" s="4">
+        <v>50</v>
+      </c>
       <c r="E11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="4">
-        <v>50</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="4">
-        <v>50</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1422,10 +1630,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -1438,12 +1646,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1478,7 +1686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>102</v>
       </c>
@@ -1497,13 +1705,13 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1530,12 +1738,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>39</v>
@@ -1551,44 +1759,52 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="K5" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>20</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3"/>
       <c r="G7" s="4"/>
@@ -1597,15 +1813,15 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -1616,47 +1832,43 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
       <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
@@ -1664,24 +1876,22 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4">
-        <v>50</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="3"/>
@@ -1689,22 +1899,24 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D12" s="4">
+        <v>50</v>
+      </c>
       <c r="E12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="3"/>
@@ -1712,30 +1924,53 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="4">
-        <v>50</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <v>50</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1743,10 +1978,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -1759,12 +1994,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1799,15 +2034,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -1818,76 +2053,78 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4">
-        <v>20</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3"/>
@@ -1897,19 +2134,17 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4">
-        <v>20</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="3"/>
       <c r="G7" s="4"/>
@@ -1918,19 +2153,17 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4">
-        <v>20</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="3"/>
       <c r="G8" s="4"/>
@@ -1939,7 +2172,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -1964,7 +2197,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
@@ -1987,7 +2220,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>31</v>
       </c>
@@ -2012,7 +2245,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
@@ -2035,7 +2268,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -2059,6 +2292,310 @@
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3182D5-E992-4F10-9BA9-EA3D1063629B}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="4.75" customWidth="1"/>
+    <col min="10" max="11" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>50</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4">
+        <v>200</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="4">
+        <v>50</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="5">
+        <v>50</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2067,9 +2604,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -2082,12 +2619,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2122,12 +2659,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -2141,24 +2678,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>15</v>
@@ -2170,17 +2707,19 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>100</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
@@ -2189,18 +2728,18 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3"/>
@@ -2210,7 +2749,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -2235,7 +2774,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -2258,7 +2797,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
@@ -2283,7 +2822,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
@@ -2306,7 +2845,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
@@ -2338,9 +2877,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -2353,12 +2892,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2393,12 +2932,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -2412,27 +2951,27 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
@@ -2443,23 +2982,25 @@
         <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
@@ -2468,95 +3009,87 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
       <c r="G6" s="4"/>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="4"/>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="4">
-        <v>50</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>33</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
       <c r="E9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
@@ -2564,30 +3097,101 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4">
-        <v>50</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4">
+        <v>50</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="4">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2596,9 +3200,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -2611,12 +3215,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2651,7 +3255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -2659,7 +3263,7 @@
         <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -2670,56 +3274,46 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D4" s="4">
+        <v>20</v>
+      </c>
       <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4">
-        <v>20</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
@@ -2728,18 +3322,18 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3"/>
@@ -2749,206 +3343,126 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="4">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="3"/>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4">
-        <v>10</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="4">
-        <v>50</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4">
-        <v>50</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2957,9 +3471,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -2972,12 +3486,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3012,7 +3526,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -3031,24 +3545,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>39</v>
@@ -3062,24 +3576,18 @@
         <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>67</v>
@@ -3093,7 +3601,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -3118,7 +3626,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -3141,7 +3649,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
@@ -3166,7 +3674,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
@@ -3189,7 +3697,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
@@ -3221,9 +3729,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -3236,12 +3744,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3276,15 +3784,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -3295,39 +3803,49 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="4">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
@@ -3343,12 +3861,12 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
@@ -3364,17 +3882,19 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>20</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3"/>
       <c r="G7" s="4"/>
@@ -3383,15 +3903,15 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -3402,19 +3922,17 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4">
-        <v>10</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="3"/>
       <c r="G9" s="4"/>
@@ -3423,30 +3941,28 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
@@ -3471,7 +3987,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -3494,7 +4010,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
@@ -3519,7 +4035,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
@@ -3542,7 +4058,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
@@ -3574,9 +4090,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -3589,12 +4105,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3629,12 +4145,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -3648,78 +4164,86 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
       <c r="E6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="3"/>
@@ -3727,24 +4251,22 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4">
-        <v>50</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3"/>
@@ -3752,22 +4274,24 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D8" s="4">
+        <v>50</v>
+      </c>
       <c r="E8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
@@ -3775,30 +4299,53 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4">
-        <v>50</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="4">
+        <v>50</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3807,9 +4354,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -3822,12 +4369,12 @@
     <col min="10" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3862,12 +4409,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -3881,24 +4428,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3"/>
@@ -3908,17 +4455,19 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
@@ -3927,17 +4476,19 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D6" s="4">
+        <v>20</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
@@ -3946,95 +4497,81 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="4"/>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="4">
-        <v>50</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>33</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
@@ -4042,24 +4579,24 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="3"/>
@@ -4067,6 +4604,102 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="4">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <v>50</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/db_specs/tpk_table_spec_20260321.xlsx
+++ b/db_specs/tpk_table_spec_20260321.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\tpk_mvp\db_specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323CAD56-5039-4A7B-8423-FCD7E36D6509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5DCE25-3172-49DF-ACFC-88F2A9C76999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tb_group_code" sheetId="12" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="149">
   <si>
     <t>tb_user : 사용자</t>
   </si>
@@ -188,9 +188,6 @@
   </si>
   <si>
     <t>버전</t>
-  </si>
-  <si>
-    <t>tb_exam_list : 시험 목록</t>
   </si>
   <si>
     <t>exam_key</t>
@@ -477,6 +474,26 @@
   </si>
   <si>
     <t>SMALLINT</t>
+  </si>
+  <si>
+    <t>시험년도</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>section</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>exam_year</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영역</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tb_exam_list : 시험 목록</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -893,7 +910,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -933,10 +950,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -952,7 +969,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
@@ -960,10 +977,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
@@ -983,10 +1000,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
@@ -1019,7 +1036,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="3"/>
@@ -1032,7 +1049,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -1080,7 +1097,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>29</v>
@@ -1148,7 +1165,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -1188,10 +1205,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -1205,27 +1222,27 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -1381,7 +1398,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -1421,10 +1438,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -1438,7 +1455,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
@@ -1446,10 +1463,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
@@ -1467,13 +1484,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -1486,13 +1503,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -1648,7 +1665,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -1688,10 +1705,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -1705,7 +1722,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
@@ -1740,10 +1757,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>39</v>
@@ -1759,18 +1776,18 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>39</v>
@@ -1786,18 +1803,18 @@
         <v>15</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>19</v>
@@ -1815,13 +1832,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -1834,10 +1851,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>39</v>
@@ -1996,7 +2013,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -2036,10 +2053,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -2053,7 +2070,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
@@ -2088,10 +2105,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>39</v>
@@ -2107,18 +2124,18 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
@@ -2136,13 +2153,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -2155,10 +2172,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>39</v>
@@ -2317,7 +2334,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -2357,10 +2374,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -2376,24 +2393,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
@@ -2407,7 +2424,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
@@ -2415,10 +2432,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
@@ -2438,10 +2455,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
@@ -2459,13 +2476,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -2506,7 +2523,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>29</v>
@@ -2554,7 +2571,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>29</v>
@@ -3201,7 +3218,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -3217,7 +3234,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -3257,10 +3274,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -3274,7 +3291,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
@@ -3282,16 +3299,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>15</v>
@@ -3305,16 +3322,20 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
@@ -3324,17 +3345,15 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4">
-        <v>10</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
@@ -3345,23 +3364,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="4"/>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
@@ -3370,21 +3385,21 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>145</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D8" s="4">
+        <v>20</v>
+      </c>
       <c r="E8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
@@ -3393,22 +3408,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
@@ -3418,10 +3433,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>29</v>
@@ -3441,10 +3456,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>19</v>
@@ -3463,6 +3478,54 @@
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="4">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3488,7 +3551,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -3528,10 +3591,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -3545,24 +3608,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>39</v>
@@ -3576,7 +3639,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
@@ -3584,13 +3647,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -3746,7 +3809,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -3786,10 +3849,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -3803,24 +3866,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>39</v>
@@ -3834,7 +3897,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
@@ -3842,10 +3905,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
@@ -3863,10 +3926,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
@@ -3884,10 +3947,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>19</v>
@@ -3905,13 +3968,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -3924,10 +3987,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>39</v>
@@ -3943,10 +4006,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -4107,7 +4170,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -4147,10 +4210,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>39</v>
@@ -4164,24 +4227,24 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>39</v>
@@ -4195,27 +4258,27 @@
         <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -4371,7 +4434,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -4411,10 +4474,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -4428,7 +4491,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3"/>
@@ -4436,10 +4499,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
@@ -4457,10 +4520,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
@@ -4478,10 +4541,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
@@ -4499,13 +4562,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -4518,10 +4581,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>39</v>
@@ -4537,10 +4600,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -4558,10 +4621,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>

--- a/db_specs/tpk_table_spec_20260321.xlsx
+++ b/db_specs/tpk_table_spec_20260321.xlsx
@@ -4463,7 +4463,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>topic_level</t>
+          <t>tpk_level</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">

--- a/db_specs/tpk_table_spec_20260321.xlsx
+++ b/db_specs/tpk_table_spec_20260321.xlsx
@@ -4700,7 +4700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4975,12 +4975,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>del_yn</t>
+          <t>file_type</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>삭제여부</t>
+          <t>파일유형</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4989,18 +4989,10 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>'N'</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="4" t="n"/>
@@ -5010,20 +5002,22 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ins_date</t>
+          <t>del_yn</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>등록일시</t>
+          <t>삭제여부</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5031,7 +5025,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>'N'</t>
         </is>
       </c>
       <c r="G10" s="4" t="n"/>
@@ -5043,22 +5037,20 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ins_user</t>
+          <t>ins_date</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>등록자</t>
+          <t>등록일시</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>50</v>
-      </c>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5066,7 +5058,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>'admin'</t>
+          <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="G11" s="4" t="n"/>
@@ -5074,6 +5066,41 @@
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ins_user</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>등록자</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>'admin'</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/db_specs/tpk_table_spec_20260321.xlsx
+++ b/db_specs/tpk_table_spec_20260321.xlsx
@@ -20,6 +20,9 @@
     <sheet name="tb_question_structure" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="tb_history_exam" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="tb_history_practice" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="tb_admin" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="tb_admin_role" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="tb_api_usage" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2985,6 +2988,989 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tb_admin : 관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>PK Name</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>FK 테이블</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>FK 컬럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>admin_id</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>관리자 ID</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>PK_ADMIN</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 (bcrypt)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>255</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>admin_desc</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>del_yn</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>삭제여부</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>'N'</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ins_date</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>생성시간</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ins_user</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>생성자</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>'admin'</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>upd_date</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>수정시간</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>upd_user</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>수정자</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>'admin'</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tb_admin_role : 관리자 권한</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>PK Name</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>FK 테이블</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>FK 컬럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>role_key</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>권한 Key</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SERIAL</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>PK_ADMIN_ROLE</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>admin_id</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>관리자 ID</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TB_ADMIN</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>admin_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>role_code</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>권한 코드</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ins_date</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>생성시간</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tb_api_usage : API 사용 이력</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>PK Name</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>FK Table</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>FK Column</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>usage_key</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>API사용 Key</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SERIAL</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>PK_API_USAGE</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>admin_id</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>관리자 ID</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>api_type</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>API 유형</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ai_provider</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>AI 프로바이더</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>모델명</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>입력 토큰</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>출력 토큰</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>cost_usd</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>비용(USD)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>10,6</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>exam_key</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>시험키</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ins_date</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>생성시간</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/db_specs/tpk_table_spec_20260321.xlsx
+++ b/db_specs/tpk_table_spec_20260321.xlsx
@@ -23,6 +23,7 @@
     <sheet name="tb_admin" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="tb_admin_role" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="tb_api_usage" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="tb_practice_request" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -67,8 +68,15 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +89,14 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -105,11 +119,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -124,6 +144,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3971,6 +3997,499 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tb_practice_request : 연습문제 생성 요청</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>PK Name</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>request_key</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>요청순번(PK)</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>SERIAL</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>PK_PRACTICE_REQUEST</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>exam_type</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>시험유형 코드</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>tpk_level</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>토픽레벨 코드</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>영역 코드</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>난이도 코드</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>question_count</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>문항수</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>gen_method</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>생성방법</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>del_yn</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>삭제여부</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>ins_date</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>등록일시</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>ins_user</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>등록자</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>upd_date</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>수정일시</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>upd_user</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>수정자</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
